--- a/data/trans_dic/P37A$medicoenfermedad-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P37A$medicoenfermedad-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 8,92</t>
+          <t>5,74; 8,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,75; 9,21</t>
+          <t>5,66; 9,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,82</t>
+          <t>4,57; 7,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 12,36</t>
+          <t>7,49; 12,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 6,24</t>
+          <t>3,9; 6,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,98</t>
+          <t>5,25; 7,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,03</t>
+          <t>3,85; 6,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,05; 13,45</t>
+          <t>10,42; 13,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 7,05</t>
+          <t>5,07; 7,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 7,98</t>
+          <t>5,79; 7,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 6,74</t>
+          <t>4,48; 6,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,66; 12,47</t>
+          <t>9,77; 12,4</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,39</t>
+          <t>1,09; 2,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,25</t>
+          <t>1,79; 3,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,78</t>
+          <t>2,17; 3,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,5</t>
+          <t>4,1; 5,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,4</t>
+          <t>1,06; 2,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,4</t>
+          <t>1,72; 3,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,96</t>
+          <t>1,62; 2,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,91</t>
+          <t>3,9; 5,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,14</t>
+          <t>1,24; 2,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,05</t>
+          <t>1,97; 3,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,1</t>
+          <t>2,08; 3,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 4,93</t>
+          <t>4,21; 5,4</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,65</t>
+          <t>0,93; 3,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,85</t>
+          <t>0,23; 2,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,92</t>
+          <t>0,96; 3,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,07</t>
+          <t>3,11; 6,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,54</t>
+          <t>0,17; 1,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,97</t>
+          <t>1,36; 4,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,75</t>
+          <t>1,27; 3,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,0</t>
+          <t>3,61; 6,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,28</t>
+          <t>0,71; 2,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,02</t>
+          <t>1,02; 3,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,28</t>
+          <t>1,42; 3,34</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 5,52</t>
+          <t>3,71; 5,7</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,1</t>
+          <t>2,86; 4,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 4,37</t>
+          <t>3,01; 4,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,19</t>
+          <t>2,89; 4,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,12; 6,08</t>
+          <t>4,89; 6,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,4</t>
+          <t>2,24; 3,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 4,67</t>
+          <t>3,36; 4,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 3,7</t>
+          <t>2,47; 3,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,47</t>
+          <t>5,66; 6,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,55</t>
+          <t>2,7; 3,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 4,37</t>
+          <t>3,38; 4,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 3,66</t>
+          <t>2,83; 3,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 6,14</t>
+          <t>5,5; 6,46</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50474</t>
+          <t>54333</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88925</t>
+          <t>99848</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>139399</t>
+          <t>154181</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>59446; 92029</t>
+          <t>59189; 92446</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56064; 89779</t>
+          <t>55131; 89975</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33461; 58975</t>
+          <t>34450; 58491</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39326; 63638</t>
+          <t>43316; 69688</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>50454; 82119</t>
+          <t>51324; 81958</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69169; 106755</t>
+          <t>70207; 105758</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39227; 69918</t>
+          <t>38341; 67948</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>75945; 101588</t>
+          <t>85618; 113990</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>117759; 165543</t>
+          <t>118925; 165747</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133360; 184526</t>
+          <t>133832; 182590</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77852; 117828</t>
+          <t>78312; 118529</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>122732; 158401</t>
+          <t>136798; 173725</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102590</t>
+          <t>110897</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>90236</t>
+          <t>99892</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>192826</t>
+          <t>210790</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19035; 40489</t>
+          <t>18452; 38972</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35478; 63867</t>
+          <t>35101; 63626</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46440; 78458</t>
+          <t>45090; 78241</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>70646; 125886</t>
+          <t>91533; 133610</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16930; 38129</t>
+          <t>16907; 37284</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31212; 59785</t>
+          <t>30285; 56872</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29806; 58817</t>
+          <t>32136; 58866</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>65743; 109919</t>
+          <t>84610; 117573</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40485; 70204</t>
+          <t>40819; 68564</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72974; 113535</t>
+          <t>73239; 112095</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84403; 126017</t>
+          <t>84494; 125238</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>149538; 223281</t>
+          <t>185155; 237773</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27930</t>
+          <t>31872</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30301</t>
+          <t>35152</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58231</t>
+          <t>67024</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5165; 20124</t>
+          <t>5126; 20598</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1129; 13716</t>
+          <t>1108; 13163</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5924; 21425</t>
+          <t>5261; 21533</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19605; 39264</t>
+          <t>22165; 43784</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>803; 7351</t>
+          <t>802; 7424</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6411; 22790</t>
+          <t>6242; 22010</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6443; 20605</t>
+          <t>6951; 20611</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22972; 39613</t>
+          <t>26545; 46758</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6777; 23423</t>
+          <t>7299; 23384</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9497; 28428</t>
+          <t>9571; 28615</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15900; 35920</t>
+          <t>15531; 36622</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46576; 72124</t>
+          <t>53658; 82432</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>180994</t>
+          <t>197102</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>209462</t>
+          <t>234892</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>390456</t>
+          <t>431994</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>92818; 134187</t>
+          <t>93850; 134078</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>103312; 149427</t>
+          <t>102856; 147739</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97049; 141536</t>
+          <t>97536; 145079</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>142333; 209755</t>
+          <t>172028; 227771</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>76264; 114793</t>
+          <t>75676; 112191</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>118811; 165828</t>
+          <t>119454; 168227</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87588; 130517</t>
+          <t>87287; 128358</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>167900; 236352</t>
+          <t>211098; 258846</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180170; 236111</t>
+          <t>179404; 232890</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>239671; 304536</t>
+          <t>235396; 300330</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>194222; 252994</t>
+          <t>195524; 256551</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>333625; 435964</t>
+          <t>398492; 468617</t>
         </is>
       </c>
     </row>
